--- a/design/report-source-models/Cost of Capital.xlsx
+++ b/design/report-source-models/Cost of Capital.xlsx
@@ -1384,12 +1384,12 @@
       <c r="H8" s="1"/>
       <c r="I8" s="8">
         <f>'Beta Calcs'!I9</f>
-        <v>-11.12347052</v>
+        <v>0.4722654152</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="8">
         <f>'Beta Calcs'!I15</f>
-        <v>7.611712135</v>
+        <v>0.3617385787</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="E10" s="9">
         <f>'Beta Calcs'!F9</f>
-        <v>-1</v>
+        <v>0.04245666083</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="3" t="s">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="M19" s="19">
         <f>L20+(L20*E10)</f>
-        <v>0</v>
+        <v>0.07268364359</v>
       </c>
       <c r="N19" s="1"/>
       <c r="O19" s="2"/>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="L20" s="23">
         <f>K21+(K21*E9)</f>
-        <v>0.09132162</v>
+        <v>0.06972342</v>
       </c>
       <c r="M20" s="24"/>
       <c r="N20" s="1"/>
@@ -1796,8 +1796,8 @@
       <c r="I21" s="20"/>
       <c r="J21" s="20"/>
       <c r="K21" s="27">
-        <f>E6+E7*E8</f>
-        <v>0.085748</v>
+        <f>E6+E8*(E7-E6)</f>
+        <v>0.065468</v>
       </c>
       <c r="L21" s="20"/>
       <c r="M21" s="24"/>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="I23" s="27">
         <f>H23*M19</f>
-        <v>0</v>
+        <v>0.04542727725</v>
       </c>
       <c r="J23" s="20"/>
       <c r="K23" s="20"/>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="E26" s="36">
         <f>I23+L24</f>
-        <v>0.0162</v>
+        <v>0.06162727725</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -29695,7 +29695,7 @@
       </c>
       <c r="F9" s="53">
         <f>AE42</f>
-        <v>-1</v>
+        <v>0.04245666083</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="3" t="s">
@@ -29703,7 +29703,7 @@
       </c>
       <c r="I9" s="54">
         <f>F9/F10</f>
-        <v>-11.12347052</v>
+        <v>0.4722654152</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -30003,7 +30003,7 @@
       </c>
       <c r="F15" s="69">
         <f>P62</f>
-        <v>0.2766719466</v>
+        <v>0.013148542</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="3" t="s">
@@ -30011,7 +30011,7 @@
       </c>
       <c r="I15" s="54">
         <f>F15/F16</f>
-        <v>7.611712135</v>
+        <v>0.3617385787</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -31173,8 +31173,8 @@
       <c r="AC40" s="2"/>
       <c r="AD40" s="50"/>
       <c r="AE40" s="95">
-        <f>X40-M40</f>
-        <v>-2569800</v>
+        <f>LOOKUP(2,1/(M40:X40&lt;&gt;""),M40:X40)-M40</f>
+        <v>109105.127</v>
       </c>
       <c r="AF40" s="11"/>
       <c r="AG40" s="1"/>
@@ -31279,7 +31279,7 @@
       <c r="AD42" s="50"/>
       <c r="AE42" s="98">
         <f>AE40/M40</f>
-        <v>-1</v>
+        <v>0.04245666083</v>
       </c>
       <c r="AF42" s="10" t="s">
         <v>53</v>
@@ -31304,7 +31304,7 @@
         <v>54</v>
       </c>
       <c r="M43" s="99">
-        <f t="shared" ref="M43:X43" si="9">if(M40=0,0,M40/M41)</f>
+        <f t="shared" ref="M43:X43" si="9">if(M40="","",M40/M41)</f>
         <v>335.9215686</v>
       </c>
       <c r="N43" s="99">
@@ -31347,9 +31347,9 @@
         <f t="shared" si="9"/>
         <v>350.1836767</v>
       </c>
-      <c r="X43" s="99">
+      <c t="str" r="X43" s="99">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y43" s="62">
         <f>SUM(M43:X43)</f>
@@ -31459,52 +31459,52 @@
         <v>32</v>
       </c>
       <c r="M46" s="66">
-        <f t="shared" ref="M46:X46" si="10">($Y$17-$M$29)</f>
-        <v>4490.938659</v>
+        <f t="shared" ref="M46:X46" si="10">($Y$50-$M$62)</f>
+        <v>338.4980905</v>
       </c>
       <c r="N46" s="66">
         <f t="shared" si="10"/>
-        <v>4490.938659</v>
+        <v>338.4980905</v>
       </c>
       <c r="O46" s="66">
         <f t="shared" si="10"/>
-        <v>4490.938659</v>
+        <v>338.4980905</v>
       </c>
       <c r="P46" s="66">
         <f t="shared" si="10"/>
-        <v>4490.938659</v>
+        <v>338.4980905</v>
       </c>
       <c r="Q46" s="66">
         <f t="shared" si="10"/>
-        <v>4490.938659</v>
+        <v>338.4980905</v>
       </c>
       <c r="R46" s="66">
         <f t="shared" si="10"/>
-        <v>4490.938659</v>
+        <v>338.4980905</v>
       </c>
       <c r="S46" s="66">
         <f t="shared" si="10"/>
-        <v>4490.938659</v>
+        <v>338.4980905</v>
       </c>
       <c r="T46" s="66">
         <f t="shared" si="10"/>
-        <v>4490.938659</v>
+        <v>338.4980905</v>
       </c>
       <c r="U46" s="66">
         <f t="shared" si="10"/>
-        <v>4490.938659</v>
+        <v>338.4980905</v>
       </c>
       <c r="V46" s="66">
         <f t="shared" si="10"/>
-        <v>4490.938659</v>
+        <v>338.4980905</v>
       </c>
       <c r="W46" s="66">
         <f t="shared" si="10"/>
-        <v>4490.938659</v>
+        <v>338.4980905</v>
       </c>
       <c r="X46" s="66">
         <f t="shared" si="10"/>
-        <v>4490.938659</v>
+        <v>338.4980905</v>
       </c>
       <c r="Y46" s="67"/>
       <c r="Z46" s="50"/>
@@ -31571,52 +31571,52 @@
         <v>35</v>
       </c>
       <c r="M48" s="66">
-        <f t="shared" ref="M48:X48" si="11">$Y$17+$M$29</f>
-        <v>4829.728007</v>
+        <f t="shared" ref="M48:X48" si="11">$Y$50+$M$62</f>
+        <v>347.5182045</v>
       </c>
       <c r="N48" s="66">
         <f t="shared" si="11"/>
-        <v>4829.728007</v>
+        <v>347.5182045</v>
       </c>
       <c r="O48" s="66">
         <f t="shared" si="11"/>
-        <v>4829.728007</v>
+        <v>347.5182045</v>
       </c>
       <c r="P48" s="66">
         <f t="shared" si="11"/>
-        <v>4829.728007</v>
+        <v>347.5182045</v>
       </c>
       <c r="Q48" s="66">
         <f t="shared" si="11"/>
-        <v>4829.728007</v>
+        <v>347.5182045</v>
       </c>
       <c r="R48" s="66">
         <f t="shared" si="11"/>
-        <v>4829.728007</v>
+        <v>347.5182045</v>
       </c>
       <c r="S48" s="66">
         <f t="shared" si="11"/>
-        <v>4829.728007</v>
+        <v>347.5182045</v>
       </c>
       <c r="T48" s="66">
         <f t="shared" si="11"/>
-        <v>4829.728007</v>
+        <v>347.5182045</v>
       </c>
       <c r="U48" s="66">
         <f t="shared" si="11"/>
-        <v>4829.728007</v>
+        <v>347.5182045</v>
       </c>
       <c r="V48" s="66">
         <f t="shared" si="11"/>
-        <v>4829.728007</v>
+        <v>347.5182045</v>
       </c>
       <c r="W48" s="66">
         <f t="shared" si="11"/>
-        <v>4829.728007</v>
+        <v>347.5182045</v>
       </c>
       <c r="X48" s="66">
         <f t="shared" si="11"/>
-        <v>4829.728007</v>
+        <v>347.5182045</v>
       </c>
       <c r="Y48" s="67"/>
       <c r="Z48" s="50"/>
@@ -31798,56 +31798,56 @@
         <v>38</v>
       </c>
       <c r="M52" s="73">
-        <f t="shared" ref="M52:X52" si="13">if(M43=0,0,$Y$17-M43)</f>
-        <v>4324.411765</v>
+        <f t="shared" ref="M52:X52" si="13">if(M43="","",$Y$50-M43)</f>
+        <v>7.086578871</v>
       </c>
       <c r="N52" s="73">
         <f t="shared" si="13"/>
-        <v>4323.012092</v>
+        <v>5.686905668</v>
       </c>
       <c r="O52" s="73">
         <f t="shared" si="13"/>
-        <v>4321.606586</v>
+        <v>4.28140044</v>
       </c>
       <c r="P52" s="73">
         <f t="shared" si="13"/>
-        <v>4320.195225</v>
+        <v>2.870039002</v>
       </c>
       <c r="Q52" s="73">
         <f t="shared" si="13"/>
-        <v>4318.777983</v>
+        <v>1.45279691</v>
       </c>
       <c r="R52" s="73">
         <f t="shared" si="13"/>
-        <v>4317.354835</v>
+        <v>0.02964959002</v>
       </c>
       <c r="S52" s="73">
         <f t="shared" si="13"/>
-        <v>4315.925758</v>
+        <v>-1.399427403</v>
       </c>
       <c r="T52" s="73">
         <f t="shared" si="13"/>
-        <v>4314.490727</v>
+        <v>-2.834459037</v>
       </c>
       <c r="U52" s="73">
         <f t="shared" si="13"/>
-        <v>4313.049716</v>
+        <v>-4.275469887</v>
       </c>
       <c r="V52" s="73">
         <f t="shared" si="13"/>
-        <v>4311.602701</v>
+        <v>-5.72248492</v>
       </c>
       <c r="W52" s="73">
         <f t="shared" si="13"/>
-        <v>4310.149657</v>
+        <v>-7.175529234</v>
       </c>
-      <c r="X52" s="73">
+      <c t="str" r="X52" s="73">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y52" s="74">
         <f>sum(M52:X52)</f>
-        <v>47490.57704</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="50"/>
       <c r="AA52" s="51"/>
@@ -31913,56 +31913,56 @@
         <v>41</v>
       </c>
       <c r="M54" s="73">
-        <f t="shared" ref="M54:X54" si="14">power(M52,2)</f>
-        <v>18700537.11</v>
+        <f t="shared" ref="M54:X54" si="14">if(M52="","",power(M52,2))</f>
+        <v>50.2196001</v>
       </c>
       <c r="N54" s="73">
         <f t="shared" si="14"/>
-        <v>18688433.54</v>
+        <v>32.34089608</v>
       </c>
       <c r="O54" s="73">
         <f t="shared" si="14"/>
-        <v>18676283.49</v>
+        <v>18.33038972</v>
       </c>
       <c r="P54" s="73">
         <f t="shared" si="14"/>
-        <v>18664086.78</v>
+        <v>8.237123872</v>
       </c>
       <c r="Q54" s="73">
         <f t="shared" si="14"/>
-        <v>18651843.26</v>
+        <v>2.110618863</v>
       </c>
       <c r="R54" s="73">
         <f t="shared" si="14"/>
-        <v>18639552.78</v>
+        <v>0.0008790981882</v>
       </c>
       <c r="S54" s="73">
         <f t="shared" si="14"/>
-        <v>18627215.15</v>
+        <v>1.958397058</v>
       </c>
       <c r="T54" s="73">
         <f t="shared" si="14"/>
-        <v>18614830.23</v>
+        <v>8.034158035</v>
       </c>
       <c r="U54" s="73">
         <f t="shared" si="14"/>
-        <v>18602397.85</v>
+        <v>18.27964276</v>
       </c>
       <c r="V54" s="73">
         <f t="shared" si="14"/>
-        <v>18589917.85</v>
+        <v>32.74683366</v>
       </c>
       <c r="W54" s="73">
         <f t="shared" si="14"/>
-        <v>18577390.06</v>
+        <v>51.48821978</v>
       </c>
-      <c r="X54" s="73">
+      <c t="str" r="X54" s="73">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y54" s="74">
         <f>sum(M54:X54)</f>
-        <v>205032488.1</v>
+        <v>223.746759</v>
       </c>
       <c r="Z54" s="50"/>
       <c r="AA54" s="51"/>
@@ -32029,7 +32029,7 @@
       </c>
       <c r="M56" s="76">
         <f>sqrt(AA56)</f>
-        <v>4317.327542</v>
+        <v>4.510057035</v>
       </c>
       <c r="N56" s="66"/>
       <c r="O56" s="66"/>
@@ -32046,7 +32046,7 @@
       <c r="Z56" s="50"/>
       <c r="AA56" s="77">
         <f>Y54/M37</f>
-        <v>18639317.1</v>
+        <v>20.34061446</v>
       </c>
       <c r="AB56" s="50"/>
       <c r="AC56" s="2"/>
@@ -32259,7 +32259,7 @@
       </c>
       <c r="M62" s="81">
         <f>_xlfn.stdev.p(M43:X43)</f>
-        <v>94.90073186</v>
+        <v>4.510057035</v>
       </c>
       <c r="N62" s="82">
         <v>0.68</v>
@@ -32267,7 +32267,7 @@
       <c r="O62" s="55"/>
       <c r="P62" s="83">
         <f>M62/Y50</f>
-        <v>0.2766719466</v>
+        <v>0.013148542</v>
       </c>
       <c r="Q62" s="55"/>
       <c r="R62" s="55"/>
@@ -32306,7 +32306,7 @@
       </c>
       <c r="M63" s="84">
         <f>M62*2</f>
-        <v>189.8014637</v>
+        <v>9.020114069</v>
       </c>
       <c r="N63" s="85">
         <v>0.95</v>
@@ -32350,7 +32350,7 @@
       </c>
       <c r="M64" s="84">
         <f>M62*3</f>
-        <v>284.7021956</v>
+        <v>13.5301711</v>
       </c>
       <c r="N64" s="87">
         <v>0.997</v>

--- a/design/report-source-models/Cost of Capital.xlsx
+++ b/design/report-source-models/Cost of Capital.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Beta Calcs" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1411,11 +1411,10 @@
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0.065</v>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Post Inflation and Post Real Growth removed 2026-07-29: the bond and index rates above are nominal, so inflation was counted twice, and a company's own growth is not part of its cost of capital. Cost of equity is K21 (CAPM), weighted straight into I23.</t>
+        </is>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="3" t="s">
@@ -1445,13 +1444,6 @@
       <c r="A10" s="1"/>
       <c r="B10" s="2"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="9">
-        <f>'Beta Calcs'!F9</f>
-        <v>0.04245666083</v>
-      </c>
       <c r="F10" s="1"/>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -1728,13 +1720,6 @@
       <c r="I19" s="16"/>
       <c r="J19" s="17"/>
       <c r="K19" s="17"/>
-      <c r="L19" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="M19" s="19">
-        <f>L20+(L20*E10)</f>
-        <v>0.07268364359</v>
-      </c>
       <c r="N19" s="1"/>
       <c r="O19" s="2"/>
       <c r="P19" s="1"/>
@@ -1760,13 +1745,6 @@
       <c r="H20" s="20"/>
       <c r="I20" s="20"/>
       <c r="J20" s="22"/>
-      <c r="K20" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="L20" s="23">
-        <f>K21+(K21*E9)</f>
-        <v>0.06972342</v>
-      </c>
       <c r="M20" s="24"/>
       <c r="N20" s="1"/>
       <c r="O20" s="2"/>
@@ -1863,8 +1841,8 @@
         <v>0.625</v>
       </c>
       <c r="I23" s="27">
-        <f>H23*M19</f>
-        <v>0.04542727725</v>
+        <f>H23*K21</f>
+        <v>0.0409175</v>
       </c>
       <c r="J23" s="20"/>
       <c r="K23" s="20"/>
@@ -1963,7 +1941,7 @@
       </c>
       <c r="E26" s="36">
         <f>I23+L24</f>
-        <v>0.06162727725</v>
+        <v>0.0571175</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
